--- a/historico_relatorios.xlsx
+++ b/historico_relatorios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaog\OneDrive\Desktop\Python\99 - Projeto\ProjetoTCC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA77AF3-7B13-4B84-A0EB-A03CFD4B19CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D79930C-3E3F-4ECD-AC41-9A122021709B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>ID Relatório</t>
   </si>
@@ -74,84 +74,6 @@
   </si>
   <si>
     <t>Ditado Pericial</t>
-  </si>
-  <si>
-    <t>2025_AB1234</t>
-  </si>
-  <si>
-    <t>2025_bo1234</t>
-  </si>
-  <si>
-    <t>AB1234</t>
-  </si>
-  <si>
-    <t>bo1234</t>
-  </si>
-  <si>
-    <t>Antonio da Silva</t>
-  </si>
-  <si>
-    <t>Acadepol</t>
-  </si>
-  <si>
-    <t>Colisao</t>
-  </si>
-  <si>
-    <t>Avenida da academia 100</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>Joao Menezes</t>
-  </si>
-  <si>
-    <t>joao menezes</t>
-  </si>
-  <si>
-    <t>51 DP</t>
-  </si>
-  <si>
-    <t>51 dp</t>
-  </si>
-  <si>
-    <t>O motorista estava trafegando quando um veiculo que ele desconhece invadiu sua pista causando danos na estrutura esquerda do seu veíuclo</t>
-  </si>
-  <si>
-    <t>o motorista bateu o carro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Houve danos? </t>
-  </si>
-  <si>
-    <t>teste</t>
-  </si>
-  <si>
-    <t>UAI2E84</t>
-  </si>
-  <si>
-    <t>Hyundai</t>
-  </si>
-  <si>
-    <t>HB20</t>
-  </si>
-  <si>
-    <t>Cinza</t>
-  </si>
-  <si>
-    <t>Direção, freio e luzes OK</t>
-  </si>
-  <si>
-    <t>Bons</t>
-  </si>
-  <si>
-    <t>Motorista informa que estava trafegando com seu veículo quando um outro veículo invadiu a faixa que estava gerando danos na parte traseira esquerda de seu carro. Não conseguiu anotar a placa do outro veículo.</t>
-  </si>
-  <si>
-    <t>Fuga de Local de Acidente</t>
   </si>
 </sst>
 </file>
@@ -519,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -578,103 +500,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2" t="s">
-        <v>38</v>
-      </c>
-      <c r="O2" t="s">
-        <v>39</v>
-      </c>
-      <c r="P2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>41</v>
-      </c>
-      <c r="R2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" t="s">
-        <v>35</v>
-      </c>
-      <c r="P3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>41</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/historico_relatorios.xlsx
+++ b/historico_relatorios.xlsx
@@ -1,105 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaog\OneDrive\Desktop\Python\99 - Projeto\ProjetoTCC\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D79930C-3E3F-4ECD-AC41-9A122021709B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
-  <si>
-    <t>ID Relatório</t>
-  </si>
-  <si>
-    <t>Número do BO</t>
-  </si>
-  <si>
-    <t>Requisitante</t>
-  </si>
-  <si>
-    <t>Natureza</t>
-  </si>
-  <si>
-    <t>Local do Fato</t>
-  </si>
-  <si>
-    <t>Data da Ocorrência</t>
-  </si>
-  <si>
-    <t>Nome do Perito</t>
-  </si>
-  <si>
-    <t>Data da Perícia</t>
-  </si>
-  <si>
-    <t>Destinatário</t>
-  </si>
-  <si>
-    <t>Histórico da Requisição</t>
-  </si>
-  <si>
-    <t>Quesito da Perícia</t>
-  </si>
-  <si>
-    <t>Placa</t>
-  </si>
-  <si>
-    <t>Marca</t>
-  </si>
-  <si>
-    <t>Modelo</t>
-  </si>
-  <si>
-    <t>Cor</t>
-  </si>
-  <si>
-    <t>Sistemas</t>
-  </si>
-  <si>
-    <t>Pneus</t>
-  </si>
-  <si>
-    <t>Ditado Pericial</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -133,24 +69,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -440,64 +435,104 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID Relatório</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Número do BO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Requisitante</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Natureza</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Local do Fato</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Data da Ocorrência</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Nome do Perito</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Data da Perícia</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Destinatário</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Histórico da Requisição</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Quesito da Perícia</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Placa</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Cor</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Sistemas</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Pneus</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Ditado Pericial</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/historico_relatorios.xlsx
+++ b/historico_relatorios.xlsx
@@ -1,41 +1,153 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+  <si>
+    <t>ID Relatório</t>
+  </si>
+  <si>
+    <t>Número do BO</t>
+  </si>
+  <si>
+    <t>Requisitante</t>
+  </si>
+  <si>
+    <t>Natureza</t>
+  </si>
+  <si>
+    <t>Local do Fato</t>
+  </si>
+  <si>
+    <t>Data da Ocorrência</t>
+  </si>
+  <si>
+    <t>Nome do Perito</t>
+  </si>
+  <si>
+    <t>Data da Perícia</t>
+  </si>
+  <si>
+    <t>Destinatário</t>
+  </si>
+  <si>
+    <t>Histórico da Requisição</t>
+  </si>
+  <si>
+    <t>Quesito da Perícia</t>
+  </si>
+  <si>
+    <t>Placa</t>
+  </si>
+  <si>
+    <t>Marca</t>
+  </si>
+  <si>
+    <t>Modelo</t>
+  </si>
+  <si>
+    <t>Cor</t>
+  </si>
+  <si>
+    <t>Sistemas</t>
+  </si>
+  <si>
+    <t>Pneus</t>
+  </si>
+  <si>
+    <t>Ditado Pericial</t>
+  </si>
+  <si>
+    <t>2025_BO1234</t>
+  </si>
+  <si>
+    <t>BO1234</t>
+  </si>
+  <si>
+    <t>Dr. Delegado de Polícia</t>
+  </si>
+  <si>
+    <t>Colisão entre veículos</t>
+  </si>
+  <si>
+    <t>Avenida da Academia, 100</t>
+  </si>
+  <si>
+    <t>2025-09-04</t>
+  </si>
+  <si>
+    <t>João Menezes</t>
+  </si>
+  <si>
+    <t>2025-09-17</t>
+  </si>
+  <si>
+    <t>51 DP</t>
+  </si>
+  <si>
+    <t>Consta no histórico que houve um choque entre dois veículos em pista de rolamento de faixa dupla. Não houve vítimas, apenas danos materiais.</t>
+  </si>
+  <si>
+    <t>Houve danos?</t>
+  </si>
+  <si>
+    <t>UAI2E84</t>
+  </si>
+  <si>
+    <t>Hiunday</t>
+  </si>
+  <si>
+    <t>HB20S</t>
+  </si>
+  <si>
+    <t>Prata</t>
+  </si>
+  <si>
+    <t>Direção, freio e luzes OK</t>
+  </si>
+  <si>
+    <t>Bons</t>
+  </si>
+  <si>
+    <t>Motorista informa que estava trafegando em sua pista de rolagem quando um outro veículo invadiu a faixa que estava gerando danos na parte traseira esquerda do seu carro. Não conseguiu anotar a placa do outro veículo. É possível verificar que marcas de tinta do outro automóvel estavam presentes no dano.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -69,90 +181,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -190,7 +235,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -224,7 +269,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -259,10 +303,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -435,104 +478,120 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:R2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ID Relatório</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Número do BO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Requisitante</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Natureza</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Local do Fato</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Data da Ocorrência</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Nome do Perito</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Data da Perícia</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Destinatário</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Histórico da Requisição</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Quesito da Perícia</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Placa</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Cor</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Sistemas</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Pneus</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Ditado Pericial</t>
-        </is>
+    <row r="1" spans="1:18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
